--- a/DNP3/dnp3_capture_with_predictions_SL_live.xlsx
+++ b/DNP3/dnp3_capture_with_predictions_SL_live.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP62"/>
+  <dimension ref="A1:AP59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,17 +657,17 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1781814729.953731</v>
+        <v>1781983090.83756</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
       <c r="I2" s="2" t="inlineStr"/>
@@ -688,22 +688,22 @@
         <v>128</v>
       </c>
       <c r="N2" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O2" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P2" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>55549</v>
+        <v>44659</v>
       </c>
       <c r="T2" s="2" t="n">
         <v>0</v>
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="W2" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z2" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB2" s="2" t="n">
         <v>1</v>
@@ -744,43 +744,43 @@
         <v>4</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG2" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH2" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0f7c6810000c3a7</t>
+          <t>056411c401000200c35ac4c4013c02063c03063c0406b10e</t>
         </is>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DNP3_RECON</t>
         </is>
       </c>
       <c r="AL2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.23</v>
       </c>
       <c r="AM2" s="2" t="n">
         <v>0.05</v>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.01</v>
+        <v>0.37</v>
       </c>
       <c r="AO2" s="2" t="n">
-        <v>0.02</v>
+        <v>0.22</v>
       </c>
       <c r="AP2" s="2" t="n">
-        <v>0.06</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="3">
@@ -793,19 +793,19 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1781814730.903592</v>
+        <v>1781983091.008093</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.9498610496520996</v>
+        <v>0.1705331802368164</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.9498610496520996</v>
+        <v>0.1705331802368164</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H3" s="2" t="inlineStr"/>
       <c r="I3" s="2" t="inlineStr"/>
@@ -826,25 +826,25 @@
         <v>128</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>39106</v>
+        <v>17725</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.9498610496520996</v>
+        <v>0.1705331802368164</v>
       </c>
       <c r="U3" s="2" t="b">
         <v>1</v>
@@ -855,19 +855,19 @@
         </is>
       </c>
       <c r="W3" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X3" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z3" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="2" t="n">
         <v>1</v>
@@ -882,23 +882,23 @@
         <v>4</v>
       </c>
       <c r="AF3" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG3" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH3" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI3" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35af7c7013c02063c03063c04066567</t>
+          <t>05640a440200010010f0c5c4810000a99b</t>
         </is>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK3" s="2" t="inlineStr">
         <is>
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="AL3" s="2" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="AM3" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.34</v>
+        <v>0.05</v>
       </c>
       <c r="AO3" s="2" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="AP3" s="2" t="n">
-        <v>0.02</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4">
@@ -931,19 +931,19 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1781814730.986945</v>
+        <v>1781983091.844049</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.03321385383606</v>
+        <v>1.006489038467407</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.08335280418395996</v>
+        <v>0.8359558582305908</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
       <c r="I4" s="2" t="inlineStr"/>
@@ -964,25 +964,25 @@
         <v>128</v>
       </c>
       <c r="N4" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O4" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P4" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q4" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>42534</v>
+        <v>34147</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.08335280418395996</v>
+        <v>0.8359558582305908</v>
       </c>
       <c r="U4" s="2" t="b">
         <v>1</v>
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="W4" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X4" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z4" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA4" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" s="2" t="n">
         <v>1</v>
@@ -1020,43 +1020,43 @@
         <v>4</v>
       </c>
       <c r="AF4" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG4" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH4" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI4" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0f8c781000070d9</t>
+          <t>056411c401000200c35ac5c5013c02063c03063c0406d8f4</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.12</v>
       </c>
       <c r="AM4" s="2" t="n">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="AO4" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="AP4" s="2" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="5">
@@ -1069,19 +1069,19 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1781814731.922858</v>
+        <v>1781983091.92567</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1.96912693977356</v>
+        <v>1.088109970092773</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.9359130859375</v>
+        <v>0.08162093162536621</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
       <c r="I5" s="2" t="inlineStr"/>
@@ -1102,25 +1102,25 @@
         <v>128</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q5" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>9881</v>
+        <v>41841</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.9359130859375</v>
+        <v>0.08162093162536621</v>
       </c>
       <c r="U5" s="2" t="b">
         <v>1</v>
@@ -1131,19 +1131,19 @@
         </is>
       </c>
       <c r="W5" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X5" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" s="2" t="n">
         <v>1</v>
@@ -1158,23 +1158,23 @@
         <v>4</v>
       </c>
       <c r="AF5" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG5" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH5" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35af8c8013c02063c03063c0406d666</t>
+          <t>05640a440200010010f0c6c58100004b3c</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK5" s="2" t="inlineStr">
         <is>
@@ -1182,19 +1182,19 @@
         </is>
       </c>
       <c r="AL5" s="2" t="n">
-        <v>0.57</v>
+        <v>0.38</v>
       </c>
       <c r="AM5" s="2" t="n">
-        <v>0.03</v>
+        <v>0.27</v>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="AO5" s="2" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="AP5" s="2" t="n">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="6">
@@ -1207,19 +1207,19 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1781814731.97432</v>
+        <v>1781983092.862967</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2.020588874816895</v>
+        <v>2.025407075881958</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.05146193504333496</v>
+        <v>0.9372971057891846</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="inlineStr"/>
@@ -1240,25 +1240,25 @@
         <v>128</v>
       </c>
       <c r="N6" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O6" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O6" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P6" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q6" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>42297</v>
+        <v>17015</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.05146193504333496</v>
+        <v>0.9372971057891846</v>
       </c>
       <c r="U6" s="2" t="b">
         <v>1</v>
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="W6" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X6" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z6" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA6" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB6" s="2" t="n">
         <v>1</v>
@@ -1296,43 +1296,43 @@
         <v>4</v>
       </c>
       <c r="AF6" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG6" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH6" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI6" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0f9c881000033d9</t>
+          <t>056411c401000200c35ac6c6013c02063c03063c04061ab7</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK6" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>0.86</v>
+        <v>0.12</v>
       </c>
       <c r="AM6" s="2" t="n">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="AO6" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="AP6" s="2" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="7">
@@ -1345,19 +1345,19 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1781814732.970499</v>
+        <v>1781983092.900859</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>3.016767978668213</v>
+        <v>2.063299179077148</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.9961791038513184</v>
+        <v>0.03789210319519043</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
       <c r="I7" s="2" t="inlineStr"/>
@@ -1378,25 +1378,25 @@
         <v>128</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q7" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>15417</v>
+        <v>51590</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.9961791038513184</v>
+        <v>0.03789210319519043</v>
       </c>
       <c r="U7" s="2" t="b">
         <v>1</v>
@@ -1407,19 +1407,19 @@
         </is>
       </c>
       <c r="W7" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="2" t="n">
         <v>1</v>
@@ -1434,23 +1434,23 @@
         <v>4</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG7" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH7" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI7" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35af9c9013c02063c03063c0406bf9c</t>
+          <t>05640a440200010010f0c7c68100000c15</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK7" s="2" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AL7" s="2" t="n">
-        <v>0.57</v>
+        <v>0.4</v>
       </c>
       <c r="AM7" s="2" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="AN7" s="2" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="AO7" s="2" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="AP7" s="2" t="n">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="8">
@@ -1483,19 +1483,19 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1781814733.035368</v>
+        <v>1781983093.897107</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3.081636905670166</v>
+        <v>3.059546947479248</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.06486892700195312</v>
+        <v>0.9962477684020996</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="2" t="inlineStr"/>
@@ -1516,25 +1516,25 @@
         <v>128</v>
       </c>
       <c r="N8" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O8" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P8" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q8" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>65137</v>
+        <v>59574</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.06486892700195312</v>
+        <v>0.9962477684020996</v>
       </c>
       <c r="U8" s="2" t="b">
         <v>1</v>
@@ -1545,19 +1545,19 @@
         </is>
       </c>
       <c r="W8" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X8" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z8" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB8" s="2" t="n">
         <v>1</v>
@@ -1572,43 +1572,43 @@
         <v>4</v>
       </c>
       <c r="AF8" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG8" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH8" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI8" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0fac9810000d17e</t>
+          <t>056411c401000200c35ac7c7013c02063c03063c0406734d</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK8" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL8" s="2" t="n">
-        <v>0.86</v>
+        <v>0.1</v>
       </c>
       <c r="AM8" s="2" t="n">
-        <v>0.04</v>
+        <v>0.18</v>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="AO8" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="AP8" s="2" t="n">
-        <v>0.06</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="9">
@@ -1621,19 +1621,19 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1781814734.017882</v>
+        <v>1781983094.150098</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>4.064151048660278</v>
+        <v>3.312538146972656</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.9825141429901123</v>
+        <v>0.2529911994934082</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="2" t="inlineStr"/>
@@ -1654,25 +1654,25 @@
         <v>128</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P9" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q9" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>31948</v>
+        <v>29097</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0.9825141429901123</v>
+        <v>0.2529911994934082</v>
       </c>
       <c r="U9" s="2" t="b">
         <v>1</v>
@@ -1683,19 +1683,19 @@
         </is>
       </c>
       <c r="W9" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X9" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y9" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA9" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="2" t="n">
         <v>1</v>
@@ -1710,43 +1710,43 @@
         <v>4</v>
       </c>
       <c r="AF9" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG9" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH9" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI9" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35afaca013c02063c03063c04067ddf</t>
+          <t>05640a440200010010f0c8c7810000bf6b</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK9" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL9" s="2" t="n">
-        <v>0.57</v>
+        <v>0.21</v>
       </c>
       <c r="AM9" s="2" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="AN9" s="2" t="n">
-        <v>0.34</v>
+        <v>0.04</v>
       </c>
       <c r="AO9" s="2" t="n">
-        <v>0.04</v>
+        <v>0.23</v>
       </c>
       <c r="AP9" s="2" t="n">
-        <v>0.02</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="10">
@@ -1759,19 +1759,19 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1781814734.27283</v>
+        <v>1781983094.916171</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4.319098949432373</v>
+        <v>4.078611135482788</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.2549479007720947</v>
+        <v>0.7660729885101318</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="2" t="inlineStr"/>
@@ -1792,25 +1792,25 @@
         <v>128</v>
       </c>
       <c r="N10" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O10" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P10" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q10" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>9347</v>
+        <v>39565</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>0.2549479007720947</v>
+        <v>0.7660729885101318</v>
       </c>
       <c r="U10" s="2" t="b">
         <v>1</v>
@@ -1821,19 +1821,19 @@
         </is>
       </c>
       <c r="W10" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X10" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z10" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10" s="2" t="n">
         <v>1</v>
@@ -1848,43 +1848,43 @@
         <v>4</v>
       </c>
       <c r="AF10" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH10" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI10" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0fbca8100009657</t>
+          <t>056411c401000200c35ac8c8013c02063c03063c0406c04c</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK10" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL10" s="2" t="n">
-        <v>0.86</v>
+        <v>0.1</v>
       </c>
       <c r="AM10" s="2" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="AN10" s="2" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="AO10" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="AP10" s="2" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="11">
@@ -1897,19 +1897,19 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1781814735.026578</v>
+        <v>1781983095.12216</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>5.07284688949585</v>
+        <v>4.284600019454956</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.7537479400634766</v>
+        <v>0.205988883972168</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
       <c r="I11" s="2" t="inlineStr"/>
@@ -1930,25 +1930,25 @@
         <v>128</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q11" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>197</v>
+        <v>231</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>58716</v>
+        <v>28738</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>0.7537479400634766</v>
+        <v>0.205988883972168</v>
       </c>
       <c r="U11" s="2" t="b">
         <v>1</v>
@@ -1959,19 +1959,19 @@
         </is>
       </c>
       <c r="W11" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X11" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y11" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA11" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" s="2" t="n">
         <v>1</v>
@@ -1986,43 +1986,43 @@
         <v>4</v>
       </c>
       <c r="AF11" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG11" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH11" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI11" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35afbcb013c02063c03063c04061425</t>
+          <t>05640a440200010010f0c9c8810000fc6b</t>
         </is>
       </c>
       <c r="AJ11" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK11" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL11" s="2" t="n">
-        <v>0.57</v>
+        <v>0.21</v>
       </c>
       <c r="AM11" s="2" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="AN11" s="2" t="n">
-        <v>0.34</v>
+        <v>0.04</v>
       </c>
       <c r="AO11" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AP11" s="2" t="n">
-        <v>0.02</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="12">
@@ -2035,19 +2035,19 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1781814735.219885</v>
+        <v>1781983095.94931</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5.266154050827026</v>
+        <v>5.11175012588501</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.1933071613311768</v>
+        <v>0.8271501064300537</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
       <c r="I12" s="2" t="inlineStr"/>
@@ -2068,25 +2068,25 @@
         <v>128</v>
       </c>
       <c r="N12" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O12" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O12" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P12" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q12" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>65154</v>
+        <v>45049</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>0.1933071613311768</v>
+        <v>0.8271501064300537</v>
       </c>
       <c r="U12" s="2" t="b">
         <v>1</v>
@@ -2097,19 +2097,19 @@
         </is>
       </c>
       <c r="W12" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z12" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12" s="2" t="n">
         <v>1</v>
@@ -2124,43 +2124,43 @@
         <v>4</v>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG12" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH12" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI12" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0fccb8100006c7c</t>
+          <t>056411c401000200c35ac9c9013c02063c03063c0406a9b6</t>
         </is>
       </c>
       <c r="AJ12" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK12" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL12" s="2" t="n">
-        <v>0.86</v>
+        <v>0.08</v>
       </c>
       <c r="AM12" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN12" s="2" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="AO12" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="AP12" s="2" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="13">
@@ -2173,19 +2173,19 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1781814736.056453</v>
+        <v>1781983096.07462</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6.102721929550171</v>
+        <v>5.237060070037842</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.8365678787231445</v>
+        <v>0.125309944152832</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
       <c r="I13" s="2" t="inlineStr"/>
@@ -2206,25 +2206,25 @@
         <v>128</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q13" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>65278</v>
+        <v>3831</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>0.8365678787231445</v>
+        <v>0.125309944152832</v>
       </c>
       <c r="U13" s="2" t="b">
         <v>1</v>
@@ -2235,19 +2235,19 @@
         </is>
       </c>
       <c r="W13" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X13" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y13" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" s="2" t="n">
         <v>1</v>
@@ -2262,23 +2262,23 @@
         <v>4</v>
       </c>
       <c r="AF13" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG13" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH13" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI13" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35afccc013c02063c03063c0406f958</t>
+          <t>05640a440200010010f0cac98100001ecc</t>
         </is>
       </c>
       <c r="AJ13" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK13" s="2" t="inlineStr">
         <is>
@@ -2286,19 +2286,19 @@
         </is>
       </c>
       <c r="AL13" s="2" t="n">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="AM13" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="AN13" s="2" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="AO13" s="2" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="AP13" s="2" t="n">
-        <v>0.02</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="14">
@@ -2311,19 +2311,19 @@
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1781814736.122229</v>
+        <v>1781983096.983141</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6.168498039245605</v>
+        <v>6.145581007003784</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.06577610969543457</v>
+        <v>0.9085209369659424</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
       <c r="I14" s="2" t="inlineStr"/>
@@ -2344,25 +2344,25 @@
         <v>128</v>
       </c>
       <c r="N14" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O14" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O14" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P14" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q14" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>61636</v>
+        <v>60560</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>0.06577610969543457</v>
+        <v>0.9085209369659424</v>
       </c>
       <c r="U14" s="2" t="b">
         <v>1</v>
@@ -2373,19 +2373,19 @@
         </is>
       </c>
       <c r="W14" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X14" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z14" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB14" s="2" t="n">
         <v>1</v>
@@ -2400,43 +2400,43 @@
         <v>4</v>
       </c>
       <c r="AF14" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG14" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH14" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI14" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0fdcc8100000089</t>
+          <t>056411c401000200c35acaca013c02063c03063c04066bf5</t>
         </is>
       </c>
       <c r="AJ14" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK14" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL14" s="2" t="n">
-        <v>0.86</v>
+        <v>0.08</v>
       </c>
       <c r="AM14" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN14" s="2" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="AO14" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="AP14" s="2" t="n">
-        <v>0.06</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="15">
@@ -2449,19 +2449,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1781814737.076117</v>
+        <v>1781983097.040421</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>7.12238597869873</v>
+        <v>6.202861070632935</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.953887939453125</v>
+        <v>0.05728006362915039</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
       <c r="I15" s="2" t="inlineStr"/>
@@ -2482,25 +2482,25 @@
         <v>128</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P15" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q15" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>26251</v>
+        <v>62609</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>0.953887939453125</v>
+        <v>0.05728006362915039</v>
       </c>
       <c r="U15" s="2" t="b">
         <v>1</v>
@@ -2511,19 +2511,19 @@
         </is>
       </c>
       <c r="W15" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X15" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y15" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z15" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA15" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" s="2" t="n">
         <v>1</v>
@@ -2538,23 +2538,23 @@
         <v>4</v>
       </c>
       <c r="AF15" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG15" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH15" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI15" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35afdcd013c02063c03063c040690a2</t>
+          <t>05640a440200010010f0cbca81000059e5</t>
         </is>
       </c>
       <c r="AJ15" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK15" s="2" t="inlineStr">
         <is>
@@ -2562,19 +2562,19 @@
         </is>
       </c>
       <c r="AL15" s="2" t="n">
-        <v>0.57</v>
+        <v>0.41</v>
       </c>
       <c r="AM15" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="AN15" s="2" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="AO15" s="2" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="AP15" s="2" t="n">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="16">
@@ -2587,19 +2587,19 @@
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1781814737.312521</v>
+        <v>1781983098.017154</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7.358789920806885</v>
+        <v>7.179594039916992</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.2364039421081543</v>
+        <v>0.9767329692840576</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
       <c r="I16" s="2" t="inlineStr"/>
@@ -2620,25 +2620,25 @@
         <v>128</v>
       </c>
       <c r="N16" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O16" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O16" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P16" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q16" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>184</v>
+        <v>235</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>18873</v>
+        <v>21837</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>0.2364039421081543</v>
+        <v>0.9767329692840576</v>
       </c>
       <c r="U16" s="2" t="b">
         <v>1</v>
@@ -2649,19 +2649,19 @@
         </is>
       </c>
       <c r="W16" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X16" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z16" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA16" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB16" s="2" t="n">
         <v>1</v>
@@ -2676,43 +2676,43 @@
         <v>4</v>
       </c>
       <c r="AF16" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG16" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH16" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI16" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0fecd810000e22e</t>
+          <t>056411c401000200c35acbcb013c02063c03063c0406020f</t>
         </is>
       </c>
       <c r="AJ16" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK16" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL16" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM16" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN16" s="2" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="AO16" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="AP16" s="2" t="n">
-        <v>0.06</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="17">
@@ -2725,19 +2725,19 @@
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1781814738.099492</v>
+        <v>1781983098.061861</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8.145761013031006</v>
+        <v>7.224301099777222</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.7869710922241211</v>
+        <v>0.04470705986022949</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
       <c r="I17" s="2" t="inlineStr"/>
@@ -2758,25 +2758,25 @@
         <v>128</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P17" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q17" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>41762</v>
+        <v>2590</v>
       </c>
       <c r="T17" s="2" t="n">
-        <v>0.7869710922241211</v>
+        <v>0.04470705986022949</v>
       </c>
       <c r="U17" s="2" t="b">
         <v>1</v>
@@ -2787,19 +2787,19 @@
         </is>
       </c>
       <c r="W17" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X17" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y17" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z17" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA17" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" s="2" t="n">
         <v>1</v>
@@ -2814,23 +2814,23 @@
         <v>4</v>
       </c>
       <c r="AF17" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG17" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH17" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI17" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35afece013c02063c03063c040652e1</t>
+          <t>05640a440200010010f0cccb810000a3ce</t>
         </is>
       </c>
       <c r="AJ17" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK17" s="2" t="inlineStr">
         <is>
@@ -2838,19 +2838,19 @@
         </is>
       </c>
       <c r="AL17" s="2" t="n">
-        <v>0.57</v>
+        <v>0.41</v>
       </c>
       <c r="AM17" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="AN17" s="2" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="AO17" s="2" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="AP17" s="2" t="n">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="18">
@@ -2863,19 +2863,19 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1781814738.175346</v>
+        <v>1781983099.066075</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8.221614837646484</v>
+        <v>8.228515148162842</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.07585382461547852</v>
+        <v>1.00421404838562</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
       <c r="I18" s="2" t="inlineStr"/>
@@ -2896,25 +2896,25 @@
         <v>128</v>
       </c>
       <c r="N18" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O18" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O18" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P18" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q18" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>28621</v>
+        <v>26303</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>0.07585382461547852</v>
+        <v>1.00421404838562</v>
       </c>
       <c r="U18" s="2" t="b">
         <v>1</v>
@@ -2925,19 +2925,19 @@
         </is>
       </c>
       <c r="W18" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z18" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB18" s="2" t="n">
         <v>1</v>
@@ -2952,43 +2952,43 @@
         <v>4</v>
       </c>
       <c r="AF18" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG18" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH18" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI18" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0ffce810000a507</t>
+          <t>056411c401000200c35acccc013c02063c03063c0406ef72</t>
         </is>
       </c>
       <c r="AJ18" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK18" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL18" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM18" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN18" s="2" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="AO18" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="AP18" s="2" t="n">
-        <v>0.06</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="19">
@@ -3001,19 +3001,19 @@
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1781814739.140457</v>
+        <v>1781983099.273968</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>9.186725854873657</v>
+        <v>8.436408042907715</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.9651110172271729</v>
+        <v>0.207892894744873</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
       <c r="I19" s="2" t="inlineStr"/>
@@ -3034,25 +3034,25 @@
         <v>128</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P19" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q19" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>47550</v>
+        <v>39880</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>0.9651110172271729</v>
+        <v>0.207892894744873</v>
       </c>
       <c r="U19" s="2" t="b">
         <v>1</v>
@@ -3063,19 +3063,19 @@
         </is>
       </c>
       <c r="W19" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X19" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y19" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z19" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA19" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19" s="2" t="n">
         <v>1</v>
@@ -3090,43 +3090,43 @@
         <v>4</v>
       </c>
       <c r="AF19" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG19" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH19" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI19" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35affcf013c02063c03063c04063b1b</t>
+          <t>05640a440200010010f0cdcc810000cf3b</t>
         </is>
       </c>
       <c r="AJ19" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK19" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL19" s="2" t="n">
-        <v>0.57</v>
+        <v>0.19</v>
       </c>
       <c r="AM19" s="2" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="AN19" s="2" t="n">
-        <v>0.34</v>
+        <v>0.04</v>
       </c>
       <c r="AO19" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AP19" s="2" t="n">
-        <v>0.02</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="20">
@@ -3139,19 +3139,19 @@
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1781814739.349565</v>
+        <v>1781983100.087266</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9.395833969116211</v>
+        <v>9.249706029891968</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.2091081142425537</v>
+        <v>0.8132979869842529</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
       <c r="I20" s="2" t="inlineStr"/>
@@ -3172,25 +3172,25 @@
         <v>128</v>
       </c>
       <c r="N20" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O20" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O20" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P20" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q20" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>60014</v>
+        <v>52863</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>0.2091081142425537</v>
+        <v>0.8132979869842529</v>
       </c>
       <c r="U20" s="2" t="b">
         <v>1</v>
@@ -3201,19 +3201,19 @@
         </is>
       </c>
       <c r="W20" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X20" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z20" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA20" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB20" s="2" t="n">
         <v>1</v>
@@ -3228,43 +3228,43 @@
         <v>4</v>
       </c>
       <c r="AF20" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG20" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH20" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI20" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c0cf810000d9cb</t>
+          <t>056411c401000200c35acdcd013c02063c03063c04068688</t>
         </is>
       </c>
       <c r="AJ20" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK20" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL20" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM20" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN20" s="2" t="n">
-        <v>0.01</v>
+        <v>0.16</v>
       </c>
       <c r="AO20" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="AP20" s="2" t="n">
-        <v>0.06</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="21">
@@ -3277,19 +3277,19 @@
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1781814740.165167</v>
+        <v>1781983100.155621</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>10.2114360332489</v>
+        <v>9.318061113357544</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.8156020641326904</v>
+        <v>0.06835508346557617</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
       <c r="I21" s="2" t="inlineStr"/>
@@ -3310,25 +3310,25 @@
         <v>128</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P21" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q21" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="S21" s="2" t="n">
-        <v>38288</v>
+        <v>14912</v>
       </c>
       <c r="T21" s="2" t="n">
-        <v>0.8156020641326904</v>
+        <v>0.06835508346557617</v>
       </c>
       <c r="U21" s="2" t="b">
         <v>1</v>
@@ -3339,19 +3339,19 @@
         </is>
       </c>
       <c r="W21" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X21" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y21" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA21" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="2" t="n">
         <v>1</v>
@@ -3366,43 +3366,43 @@
         <v>4</v>
       </c>
       <c r="AF21" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG21" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH21" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI21" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac0c0013c02063c03063c04069e30</t>
+          <t>05640a440200010010f0cecd8100002d9c</t>
         </is>
       </c>
       <c r="AJ21" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK21" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>CONTROL_ATTACK</t>
         </is>
       </c>
       <c r="AL21" s="2" t="n">
-        <v>0.57</v>
+        <v>0.31</v>
       </c>
       <c r="AM21" s="2" t="n">
-        <v>0.03</v>
+        <v>0.34</v>
       </c>
       <c r="AN21" s="2" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="AO21" s="2" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="AP21" s="2" t="n">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="22">
@@ -3415,19 +3415,19 @@
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1781814740.221948</v>
+        <v>1781983101.102472</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>10.26821684837341</v>
+        <v>10.26491212844849</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.05678081512451172</v>
+        <v>0.9468510150909424</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
       <c r="I22" s="2" t="inlineStr"/>
@@ -3448,25 +3448,25 @@
         <v>128</v>
       </c>
       <c r="N22" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O22" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O22" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P22" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q22" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>59795</v>
+        <v>3860</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>0.05678081512451172</v>
+        <v>0.9468510150909424</v>
       </c>
       <c r="U22" s="2" t="b">
         <v>1</v>
@@ -3477,19 +3477,19 @@
         </is>
       </c>
       <c r="W22" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X22" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z22" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB22" s="2" t="n">
         <v>1</v>
@@ -3504,43 +3504,43 @@
         <v>4</v>
       </c>
       <c r="AF22" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG22" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH22" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI22" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c1c08100009acb</t>
+          <t>056411c401000200c35acece013c02063c03063c040644cb</t>
         </is>
       </c>
       <c r="AJ22" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK22" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL22" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM22" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN22" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO22" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP22" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="23">
@@ -3553,19 +3553,19 @@
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1781814741.183239</v>
+        <v>1781983101.15772</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>11.22950792312622</v>
+        <v>10.32016015052795</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.9612910747528076</v>
+        <v>0.05524802207946777</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
       <c r="I23" s="2" t="inlineStr"/>
@@ -3586,25 +3586,25 @@
         <v>128</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P23" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q23" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>15052</v>
+        <v>8153</v>
       </c>
       <c r="T23" s="2" t="n">
-        <v>0.9612910747528076</v>
+        <v>0.05524802207946777</v>
       </c>
       <c r="U23" s="2" t="b">
         <v>1</v>
@@ -3615,19 +3615,19 @@
         </is>
       </c>
       <c r="W23" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X23" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="2" t="n">
         <v>1</v>
@@ -3642,43 +3642,43 @@
         <v>4</v>
       </c>
       <c r="AF23" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG23" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH23" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI23" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac1c1013c02063c03063c0406f7ca</t>
+          <t>05640a440200010010f0cfce8100006ab5</t>
         </is>
       </c>
       <c r="AJ23" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK23" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>CONTROL_ATTACK</t>
         </is>
       </c>
       <c r="AL23" s="2" t="n">
-        <v>0.57</v>
+        <v>0.3</v>
       </c>
       <c r="AM23" s="2" t="n">
-        <v>0.03</v>
+        <v>0.35</v>
       </c>
       <c r="AN23" s="2" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="AO23" s="2" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="AP23" s="2" t="n">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="24">
@@ -3691,19 +3691,19 @@
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1781814741.229386</v>
+        <v>1781983102.122405</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>11.27565503120422</v>
+        <v>11.28484511375427</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.04614710807800293</v>
+        <v>0.9646849632263184</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
       <c r="I24" s="2" t="inlineStr"/>
@@ -3724,25 +3724,25 @@
         <v>128</v>
       </c>
       <c r="N24" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O24" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O24" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P24" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q24" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>18316</v>
+        <v>9604</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>0.04614710807800293</v>
+        <v>0.9646849632263184</v>
       </c>
       <c r="U24" s="2" t="b">
         <v>1</v>
@@ -3753,19 +3753,19 @@
         </is>
       </c>
       <c r="W24" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X24" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z24" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB24" s="2" t="n">
         <v>1</v>
@@ -3780,43 +3780,43 @@
         <v>4</v>
       </c>
       <c r="AF24" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG24" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH24" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI24" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c2c1810000786c</t>
+          <t>056411c401000200c35acfcf013c02063c03063c04062d31</t>
         </is>
       </c>
       <c r="AJ24" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK24" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL24" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM24" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN24" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO24" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP24" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="25">
@@ -3829,19 +3829,19 @@
         <v>24</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>1781814742.197155</v>
+        <v>1781983102.371039</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>12.24342393875122</v>
+        <v>11.53347897529602</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.9677689075469971</v>
+        <v>0.248633861541748</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
       <c r="I25" s="2" t="inlineStr"/>
@@ -3862,25 +3862,25 @@
         <v>128</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q25" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>64483</v>
+        <v>29390</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>0.9677689075469971</v>
+        <v>0.248633861541748</v>
       </c>
       <c r="U25" s="2" t="b">
         <v>1</v>
@@ -3891,19 +3891,19 @@
         </is>
       </c>
       <c r="W25" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X25" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z25" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA25" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" s="2" t="n">
         <v>1</v>
@@ -3918,43 +3918,43 @@
         <v>4</v>
       </c>
       <c r="AF25" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG25" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH25" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI25" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac2c2013c02063c03063c04063589</t>
+          <t>05640a440200010010f0d0cf8100004b61</t>
         </is>
       </c>
       <c r="AJ25" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK25" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL25" s="2" t="n">
-        <v>0.57</v>
+        <v>0.13</v>
       </c>
       <c r="AM25" s="2" t="n">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="AN25" s="2" t="n">
-        <v>0.34</v>
+        <v>0.04</v>
       </c>
       <c r="AO25" s="2" t="n">
-        <v>0.04</v>
+        <v>0.23</v>
       </c>
       <c r="AP25" s="2" t="n">
-        <v>0.02</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="26">
@@ -3967,19 +3967,19 @@
         <v>25</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>1781814742.391029</v>
+        <v>1781983103.144856</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>12.43729782104492</v>
+        <v>12.30729603767395</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.1938738822937012</v>
+        <v>0.7738170623779297</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="2" t="inlineStr"/>
@@ -4000,25 +4000,25 @@
         <v>128</v>
       </c>
       <c r="N26" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O26" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O26" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P26" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q26" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>28059</v>
+        <v>38317</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>0.1938738822937012</v>
+        <v>0.7738170623779297</v>
       </c>
       <c r="U26" s="2" t="b">
         <v>1</v>
@@ -4029,19 +4029,19 @@
         </is>
       </c>
       <c r="W26" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X26" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z26" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA26" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB26" s="2" t="n">
         <v>1</v>
@@ -4056,43 +4056,43 @@
         <v>4</v>
       </c>
       <c r="AF26" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG26" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH26" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI26" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c3c28100003f45</t>
+          <t>056411c401000200c35ad0c0013c02063c03063c0406bbed</t>
         </is>
       </c>
       <c r="AJ26" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK26" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL26" s="2" t="n">
-        <v>0.86</v>
+        <v>0.08</v>
       </c>
       <c r="AM26" s="2" t="n">
-        <v>0.04</v>
+        <v>0.23</v>
       </c>
       <c r="AN26" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO26" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP26" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="27">
@@ -4105,19 +4105,19 @@
         <v>26</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>1781814743.214402</v>
+        <v>1781983103.288472</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>13.26067090034485</v>
+        <v>12.45091199874878</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.8233730792999268</v>
+        <v>0.1436159610748291</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
       <c r="I27" s="2" t="inlineStr"/>
@@ -4138,25 +4138,25 @@
         <v>128</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P27" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q27" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>54223</v>
+        <v>29175</v>
       </c>
       <c r="T27" s="2" t="n">
-        <v>0.8233730792999268</v>
+        <v>0.1436159610748291</v>
       </c>
       <c r="U27" s="2" t="b">
         <v>1</v>
@@ -4167,19 +4167,19 @@
         </is>
       </c>
       <c r="W27" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X27" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y27" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" s="2" t="n">
         <v>1</v>
@@ -4194,43 +4194,43 @@
         <v>4</v>
       </c>
       <c r="AF27" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG27" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH27" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI27" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac3c3013c02063c03063c04065c73</t>
+          <t>05640a440200010010f0d1c08100000861</t>
         </is>
       </c>
       <c r="AJ27" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK27" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>CONTROL_ATTACK</t>
         </is>
       </c>
       <c r="AL27" s="2" t="n">
-        <v>0.57</v>
+        <v>0.25</v>
       </c>
       <c r="AM27" s="2" t="n">
-        <v>0.03</v>
+        <v>0.34</v>
       </c>
       <c r="AN27" s="2" t="n">
-        <v>0.34</v>
+        <v>0.05</v>
       </c>
       <c r="AO27" s="2" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="AP27" s="2" t="n">
-        <v>0.02</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="28">
@@ -4243,19 +4243,19 @@
         <v>27</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>1781814743.29002</v>
+        <v>1781983104.154623</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>13.3362889289856</v>
+        <v>13.31706309318542</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.07561802864074707</v>
+        <v>0.8661510944366455</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
       <c r="I28" s="2" t="inlineStr"/>
@@ -4276,25 +4276,25 @@
         <v>128</v>
       </c>
       <c r="N28" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O28" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O28" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P28" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q28" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>17131</v>
+        <v>32345</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>0.07561802864074707</v>
+        <v>0.8661510944366455</v>
       </c>
       <c r="U28" s="2" t="b">
         <v>1</v>
@@ -4305,19 +4305,19 @@
         </is>
       </c>
       <c r="W28" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X28" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z28" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB28" s="2" t="n">
         <v>1</v>
@@ -4332,43 +4332,43 @@
         <v>4</v>
       </c>
       <c r="AF28" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG28" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH28" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI28" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c4c3810000c56e</t>
+          <t>056411c401000200c35ad1c1013c02063c03063c0406d217</t>
         </is>
       </c>
       <c r="AJ28" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK28" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL28" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM28" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN28" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO28" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP28" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="29">
@@ -4381,19 +4381,19 @@
         <v>28</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>1781814744.243214</v>
+        <v>1781983104.239986</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>14.28948283195496</v>
+        <v>13.40242600440979</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.9531939029693604</v>
+        <v>0.08536291122436523</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
       <c r="I29" s="2" t="inlineStr"/>
@@ -4414,25 +4414,25 @@
         <v>128</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P29" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q29" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>32266</v>
+        <v>2795</v>
       </c>
       <c r="T29" s="2" t="n">
-        <v>0.9531939029693604</v>
+        <v>0.08536291122436523</v>
       </c>
       <c r="U29" s="2" t="b">
         <v>1</v>
@@ -4443,19 +4443,19 @@
         </is>
       </c>
       <c r="W29" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X29" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y29" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z29" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA29" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" s="2" t="n">
         <v>1</v>
@@ -4470,43 +4470,43 @@
         <v>4</v>
       </c>
       <c r="AF29" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG29" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH29" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI29" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac4c4013c02063c03063c0406b10e</t>
+          <t>05640a440200010010f0d2c1810000eac6</t>
         </is>
       </c>
       <c r="AJ29" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK29" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>CONTROL_ATTACK</t>
         </is>
       </c>
       <c r="AL29" s="2" t="n">
-        <v>0.57</v>
+        <v>0.28</v>
       </c>
       <c r="AM29" s="2" t="n">
-        <v>0.03</v>
+        <v>0.37</v>
       </c>
       <c r="AN29" s="2" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="AO29" s="2" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="AP29" s="2" t="n">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="30">
@@ -4519,19 +4519,19 @@
         <v>29</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1781814744.438063</v>
+        <v>1781983105.185136</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>14.48433184623718</v>
+        <v>14.34757614135742</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.1948490142822266</v>
+        <v>0.9451501369476318</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
       <c r="I30" s="2" t="inlineStr"/>
@@ -4552,25 +4552,25 @@
         <v>128</v>
       </c>
       <c r="N30" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O30" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O30" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P30" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q30" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>5341</v>
+        <v>16115</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>0.1948490142822266</v>
+        <v>0.9451501369476318</v>
       </c>
       <c r="U30" s="2" t="b">
         <v>1</v>
@@ -4581,19 +4581,19 @@
         </is>
       </c>
       <c r="W30" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X30" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z30" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB30" s="2" t="n">
         <v>1</v>
@@ -4608,43 +4608,43 @@
         <v>4</v>
       </c>
       <c r="AF30" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG30" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH30" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI30" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c5c4810000a99b</t>
+          <t>056411c401000200c35ad2c2013c02063c03063c04061054</t>
         </is>
       </c>
       <c r="AJ30" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK30" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL30" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM30" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN30" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO30" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP30" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="31">
@@ -4657,19 +4657,19 @@
         <v>30</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1781814744.725363</v>
+        <v>1781983105.238373</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>14.77163195610046</v>
+        <v>14.40081310272217</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.2873001098632812</v>
+        <v>0.05323696136474609</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
       <c r="I31" s="2" t="inlineStr"/>
@@ -4690,25 +4690,25 @@
         <v>128</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P31" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q31" s="2" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="S31" s="2" t="n">
-        <v>3060</v>
+        <v>57597</v>
       </c>
       <c r="T31" s="2" t="n">
-        <v>0.2873001098632812</v>
+        <v>0.05323696136474609</v>
       </c>
       <c r="U31" s="2" t="b">
         <v>1</v>
@@ -4719,19 +4719,19 @@
         </is>
       </c>
       <c r="W31" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="X31" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z31" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB31" s="2" t="n">
         <v>1</v>
@@ -4746,43 +4746,43 @@
         <v>4</v>
       </c>
       <c r="AF31" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG31" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH31" s="2" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AI31" s="2" t="inlineStr">
         <is>
-          <t>056414c4010002004aa2c5c5013c01063c02063c03063c0406ad57</t>
+          <t>05640a440200010010f0d3c2810000adef</t>
         </is>
       </c>
       <c r="AJ31" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK31" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>CONTROL_ATTACK</t>
         </is>
       </c>
       <c r="AL31" s="2" t="n">
-        <v>0.57</v>
+        <v>0.29</v>
       </c>
       <c r="AM31" s="2" t="n">
-        <v>0.03</v>
+        <v>0.36</v>
       </c>
       <c r="AN31" s="2" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="AO31" s="2" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="AP31" s="2" t="n">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="32">
@@ -4795,19 +4795,19 @@
         <v>31</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>1781814744.791381</v>
+        <v>1781983106.236241</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>14.83764982223511</v>
+        <v>15.39868116378784</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.06601786613464355</v>
+        <v>0.9978680610656738</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>219</v>
+        <v>68</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>219</v>
+        <v>68</v>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
@@ -4828,25 +4828,25 @@
         <v>128</v>
       </c>
       <c r="N32" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O32" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O32" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P32" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>175</v>
+        <v>24</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>50287</v>
+        <v>54382</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>0.06601786613464355</v>
+        <v>0.9978680610656738</v>
       </c>
       <c r="U32" s="2" t="b">
         <v>1</v>
@@ -4857,19 +4857,19 @@
         </is>
       </c>
       <c r="W32" s="2" t="n">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="X32" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z32" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB32" s="2" t="n">
         <v>1</v>
@@ -4884,43 +4884,43 @@
         <v>4</v>
       </c>
       <c r="AF32" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG32" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH32" s="2" t="n">
-        <v>175</v>
+        <v>24</v>
       </c>
       <c r="AI32" s="2" t="inlineStr">
         <is>
-          <t>0564964402000100e04ec6c58100000102000009010101010101223c01010101</t>
+          <t>056411c401000200c35ad3c3013c02063c03063c040679ae</t>
         </is>
       </c>
       <c r="AJ32" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK32" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL32" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM32" s="2" t="n">
-        <v>0.05</v>
+        <v>0.22</v>
       </c>
       <c r="AN32" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO32" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP32" s="2" t="n">
-        <v>0.05</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="33">
@@ -4933,19 +4933,19 @@
         <v>32</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>1781814745.283937</v>
+        <v>1781983106.497906</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>15.3302059173584</v>
+        <v>15.66034603118896</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.492556095123291</v>
+        <v>0.261664867401123</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
@@ -4966,25 +4966,25 @@
         <v>128</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P33" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>195</v>
+        <v>230</v>
       </c>
       <c r="S33" s="2" t="n">
-        <v>4462</v>
+        <v>2858</v>
       </c>
       <c r="T33" s="2" t="n">
-        <v>0.492556095123291</v>
+        <v>0.261664867401123</v>
       </c>
       <c r="U33" s="2" t="b">
         <v>1</v>
@@ -4995,19 +4995,19 @@
         </is>
       </c>
       <c r="W33" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X33" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA33" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" s="2" t="n">
         <v>1</v>
@@ -5022,43 +5022,43 @@
         <v>4</v>
       </c>
       <c r="AF33" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG33" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH33" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI33" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac6c6013c02063c03063c04061ab7</t>
+          <t>05640a440200010010f0d4c381000057c4</t>
         </is>
       </c>
       <c r="AJ33" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK33" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL33" s="2" t="n">
-        <v>0.57</v>
+        <v>0.13</v>
       </c>
       <c r="AM33" s="2" t="n">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="AN33" s="2" t="n">
-        <v>0.34</v>
+        <v>0.04</v>
       </c>
       <c r="AO33" s="2" t="n">
-        <v>0.04</v>
+        <v>0.23</v>
       </c>
       <c r="AP33" s="2" t="n">
-        <v>0.02</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="34">
@@ -5071,19 +5071,19 @@
         <v>33</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>1781814745.368009</v>
+        <v>1781983107.256252</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>15.41427803039551</v>
+        <v>16.41869211196899</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.08407211303710938</v>
+        <v>0.7583460807800293</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
       <c r="I34" s="2" t="inlineStr"/>
@@ -5104,25 +5104,25 @@
         <v>128</v>
       </c>
       <c r="N34" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O34" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O34" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P34" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q34" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>39045</v>
+        <v>47135</v>
       </c>
       <c r="T34" s="2" t="n">
-        <v>0.08407211303710938</v>
+        <v>0.7583460807800293</v>
       </c>
       <c r="U34" s="2" t="b">
         <v>1</v>
@@ -5133,19 +5133,19 @@
         </is>
       </c>
       <c r="W34" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X34" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z34" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB34" s="2" t="n">
         <v>1</v>
@@ -5160,43 +5160,43 @@
         <v>4</v>
       </c>
       <c r="AF34" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG34" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH34" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI34" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c7c68100000c15</t>
+          <t>056411c401000200c35ad4c4013c02063c03063c040694d3</t>
         </is>
       </c>
       <c r="AJ34" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK34" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL34" s="2" t="n">
-        <v>0.86</v>
+        <v>0.08</v>
       </c>
       <c r="AM34" s="2" t="n">
-        <v>0.04</v>
+        <v>0.23</v>
       </c>
       <c r="AN34" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO34" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP34" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="35">
@@ -5209,19 +5209,19 @@
         <v>34</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1781814746.291311</v>
+        <v>1781983107.405966</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>16.33757996559143</v>
+        <v>16.5684061050415</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.9233019351959229</v>
+        <v>0.1497139930725098</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
       <c r="I35" s="2" t="inlineStr"/>
@@ -5242,25 +5242,25 @@
         <v>128</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P35" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q35" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="S35" s="2" t="n">
-        <v>47021</v>
+        <v>40221</v>
       </c>
       <c r="T35" s="2" t="n">
-        <v>0.9233019351959229</v>
+        <v>0.1497139930725098</v>
       </c>
       <c r="U35" s="2" t="b">
         <v>1</v>
@@ -5271,19 +5271,19 @@
         </is>
       </c>
       <c r="W35" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X35" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA35" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB35" s="2" t="n">
         <v>1</v>
@@ -5298,43 +5298,43 @@
         <v>4</v>
       </c>
       <c r="AF35" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG35" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH35" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI35" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac7c7013c02063c03063c0406734d</t>
+          <t>05640a440200010010f0d5c48100003b31</t>
         </is>
       </c>
       <c r="AJ35" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK35" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>CONTROL_ATTACK</t>
         </is>
       </c>
       <c r="AL35" s="2" t="n">
-        <v>0.57</v>
+        <v>0.25</v>
       </c>
       <c r="AM35" s="2" t="n">
-        <v>0.03</v>
+        <v>0.34</v>
       </c>
       <c r="AN35" s="2" t="n">
-        <v>0.34</v>
+        <v>0.05</v>
       </c>
       <c r="AO35" s="2" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="AP35" s="2" t="n">
-        <v>0.02</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="36">
@@ -5347,19 +5347,19 @@
         <v>35</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>1781814746.53118</v>
+        <v>1781983108.304682</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>16.57744884490967</v>
+        <v>17.46712207794189</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.2398688793182373</v>
+        <v>0.8987159729003906</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
@@ -5380,25 +5380,25 @@
         <v>128</v>
       </c>
       <c r="N36" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O36" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O36" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P36" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q36" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="S36" s="2" t="n">
-        <v>16552</v>
+        <v>20127</v>
       </c>
       <c r="T36" s="2" t="n">
-        <v>0.2398688793182373</v>
+        <v>0.8987159729003906</v>
       </c>
       <c r="U36" s="2" t="b">
         <v>1</v>
@@ -5409,19 +5409,19 @@
         </is>
       </c>
       <c r="W36" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X36" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z36" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA36" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB36" s="2" t="n">
         <v>1</v>
@@ -5436,43 +5436,43 @@
         <v>4</v>
       </c>
       <c r="AF36" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG36" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH36" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI36" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c8c7810000bf6b</t>
+          <t>056411c401000200c35ad5c5013c02063c03063c0406fd29</t>
         </is>
       </c>
       <c r="AJ36" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK36" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL36" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM36" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN36" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO36" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP36" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="37">
@@ -5485,19 +5485,19 @@
         <v>36</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1781814747.313077</v>
+        <v>1781983108.358716</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>17.35934591293335</v>
+        <v>17.52115607261658</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.7818970680236816</v>
+        <v>0.05403399467468262</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
@@ -5518,25 +5518,25 @@
         <v>128</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P37" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q37" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R37" s="2" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="S37" s="2" t="n">
-        <v>27012</v>
+        <v>13909</v>
       </c>
       <c r="T37" s="2" t="n">
-        <v>0.7818970680236816</v>
+        <v>0.05403399467468262</v>
       </c>
       <c r="U37" s="2" t="b">
         <v>1</v>
@@ -5547,19 +5547,19 @@
         </is>
       </c>
       <c r="W37" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X37" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y37" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z37" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA37" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB37" s="2" t="n">
         <v>1</v>
@@ -5574,43 +5574,43 @@
         <v>4</v>
       </c>
       <c r="AF37" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG37" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH37" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI37" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac8c8013c02063c03063c0406c04c</t>
+          <t>05640a440200010010f0d6c5810000d996</t>
         </is>
       </c>
       <c r="AJ37" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK37" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>CONTROL_ATTACK</t>
         </is>
       </c>
       <c r="AL37" s="2" t="n">
-        <v>0.57</v>
+        <v>0.28</v>
       </c>
       <c r="AM37" s="2" t="n">
-        <v>0.03</v>
+        <v>0.37</v>
       </c>
       <c r="AN37" s="2" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="AO37" s="2" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="AP37" s="2" t="n">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="38">
@@ -5623,19 +5623,19 @@
         <v>37</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1781814747.417573</v>
+        <v>1781983109.353207</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>17.46384191513062</v>
+        <v>18.51564717292786</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.1044960021972656</v>
+        <v>0.9944911003112793</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
@@ -5656,25 +5656,25 @@
         <v>128</v>
       </c>
       <c r="N38" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O38" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O38" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P38" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q38" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>16194</v>
+        <v>2869</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>0.1044960021972656</v>
+        <v>0.9944911003112793</v>
       </c>
       <c r="U38" s="2" t="b">
         <v>1</v>
@@ -5685,19 +5685,19 @@
         </is>
       </c>
       <c r="W38" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X38" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z38" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA38" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB38" s="2" t="n">
         <v>1</v>
@@ -5712,43 +5712,43 @@
         <v>4</v>
       </c>
       <c r="AF38" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG38" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH38" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI38" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c9c8810000fc6b</t>
+          <t>056411c401000200c35ad6c6013c02063c03063c04063f6a</t>
         </is>
       </c>
       <c r="AJ38" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK38" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL38" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM38" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN38" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO38" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP38" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="39">
@@ -5761,19 +5761,19 @@
         <v>38</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>1781814748.347802</v>
+        <v>1781983109.602633</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>18.39407086372375</v>
+        <v>18.76507306098938</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.9302289485931396</v>
+        <v>0.2494258880615234</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
@@ -5794,25 +5794,25 @@
         <v>128</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P39" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q39" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R39" s="2" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="S39" s="2" t="n">
-        <v>32496</v>
+        <v>3174</v>
       </c>
       <c r="T39" s="2" t="n">
-        <v>0.9302289485931396</v>
+        <v>0.2494258880615234</v>
       </c>
       <c r="U39" s="2" t="b">
         <v>1</v>
@@ -5823,19 +5823,19 @@
         </is>
       </c>
       <c r="W39" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X39" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y39" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z39" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA39" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39" s="2" t="n">
         <v>1</v>
@@ -5850,43 +5850,43 @@
         <v>4</v>
       </c>
       <c r="AF39" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG39" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH39" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI39" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac9c9013c02063c03063c0406a9b6</t>
+          <t>05640a440200010010f0d7c68100009ebf</t>
         </is>
       </c>
       <c r="AJ39" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK39" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL39" s="2" t="n">
-        <v>0.57</v>
+        <v>0.13</v>
       </c>
       <c r="AM39" s="2" t="n">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="AN39" s="2" t="n">
-        <v>0.34</v>
+        <v>0.04</v>
       </c>
       <c r="AO39" s="2" t="n">
-        <v>0.04</v>
+        <v>0.25</v>
       </c>
       <c r="AP39" s="2" t="n">
-        <v>0.02</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="40">
@@ -5899,19 +5899,19 @@
         <v>39</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>1781814748.586745</v>
+        <v>1781983110.399547</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>18.63301396369934</v>
+        <v>19.56198716163635</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.2389430999755859</v>
+        <v>0.7969141006469727</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
@@ -5932,25 +5932,25 @@
         <v>128</v>
       </c>
       <c r="N40" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O40" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O40" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P40" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q40" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>56821</v>
+        <v>62180</v>
       </c>
       <c r="T40" s="2" t="n">
-        <v>0.2389430999755859</v>
+        <v>0.7969141006469727</v>
       </c>
       <c r="U40" s="2" t="b">
         <v>1</v>
@@ -5961,19 +5961,19 @@
         </is>
       </c>
       <c r="W40" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X40" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z40" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA40" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB40" s="2" t="n">
         <v>1</v>
@@ -5988,43 +5988,43 @@
         <v>4</v>
       </c>
       <c r="AF40" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG40" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH40" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI40" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0cac98100001ecc</t>
+          <t>056411c401000200c35ad7c7013c02063c03063c04065690</t>
         </is>
       </c>
       <c r="AJ40" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK40" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL40" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM40" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN40" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO40" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP40" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="41">
@@ -6037,19 +6037,19 @@
         <v>40</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1781814749.370461</v>
+        <v>1781983110.520434</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>19.41672992706299</v>
+        <v>19.68287396430969</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.7837159633636475</v>
+        <v>0.1208868026733398</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
@@ -6070,25 +6070,25 @@
         <v>128</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P41" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q41" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="S41" s="2" t="n">
-        <v>48007</v>
+        <v>2477</v>
       </c>
       <c r="T41" s="2" t="n">
-        <v>0.7837159633636475</v>
+        <v>0.1208868026733398</v>
       </c>
       <c r="U41" s="2" t="b">
         <v>1</v>
@@ -6099,19 +6099,19 @@
         </is>
       </c>
       <c r="W41" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X41" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y41" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z41" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA41" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB41" s="2" t="n">
         <v>1</v>
@@ -6126,43 +6126,43 @@
         <v>4</v>
       </c>
       <c r="AF41" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG41" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH41" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI41" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35acaca013c02063c03063c04066bf5</t>
+          <t>05640a440200010010f0d8c78100002dc1</t>
         </is>
       </c>
       <c r="AJ41" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK41" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>CONTROL_ATTACK</t>
         </is>
       </c>
       <c r="AL41" s="2" t="n">
-        <v>0.57</v>
+        <v>0.28</v>
       </c>
       <c r="AM41" s="2" t="n">
-        <v>0.03</v>
+        <v>0.36</v>
       </c>
       <c r="AN41" s="2" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="AO41" s="2" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="AP41" s="2" t="n">
-        <v>0.02</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="42">
@@ -6175,19 +6175,19 @@
         <v>41</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>1781814749.467569</v>
+        <v>1781983111.433397</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>19.51383805274963</v>
+        <v>20.59583711624146</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.09710812568664551</v>
+        <v>0.9129631519317627</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
@@ -6208,25 +6208,25 @@
         <v>128</v>
       </c>
       <c r="N42" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O42" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O42" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P42" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q42" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>50064</v>
+        <v>25273</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>0.09710812568664551</v>
+        <v>0.9129631519317627</v>
       </c>
       <c r="U42" s="2" t="b">
         <v>1</v>
@@ -6237,19 +6237,19 @@
         </is>
       </c>
       <c r="W42" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X42" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z42" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB42" s="2" t="n">
         <v>1</v>
@@ -6264,43 +6264,43 @@
         <v>4</v>
       </c>
       <c r="AF42" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG42" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH42" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI42" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0cbca81000059e5</t>
+          <t>056411c401000200c35ad8c8013c02063c03063c0406e591</t>
         </is>
       </c>
       <c r="AJ42" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK42" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL42" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM42" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN42" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO42" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP42" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="43">
@@ -6313,19 +6313,19 @@
         <v>42</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>1781814750.392115</v>
+        <v>1781983111.488565</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>20.43838405609131</v>
+        <v>20.65100502967834</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.9245460033416748</v>
+        <v>0.05516791343688965</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
@@ -6346,25 +6346,25 @@
         <v>128</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P43" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q43" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R43" s="2" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="S43" s="2" t="n">
-        <v>9284</v>
+        <v>2114</v>
       </c>
       <c r="T43" s="2" t="n">
-        <v>0.9245460033416748</v>
+        <v>0.05516791343688965</v>
       </c>
       <c r="U43" s="2" t="b">
         <v>1</v>
@@ -6375,19 +6375,19 @@
         </is>
       </c>
       <c r="W43" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X43" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB43" s="2" t="n">
         <v>1</v>
@@ -6402,43 +6402,43 @@
         <v>4</v>
       </c>
       <c r="AF43" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG43" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH43" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI43" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35acbcb013c02063c03063c0406020f</t>
+          <t>05640a440200010010f0d9c88100006ec1</t>
         </is>
       </c>
       <c r="AJ43" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK43" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>CONTROL_ATTACK</t>
         </is>
       </c>
       <c r="AL43" s="2" t="n">
-        <v>0.57</v>
+        <v>0.29</v>
       </c>
       <c r="AM43" s="2" t="n">
-        <v>0.03</v>
+        <v>0.36</v>
       </c>
       <c r="AN43" s="2" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="AO43" s="2" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="AP43" s="2" t="n">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="44">
@@ -6451,19 +6451,19 @@
         <v>43</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>1781814750.459621</v>
+        <v>1781983112.465371</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>20.50588989257812</v>
+        <v>21.62781095504761</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.06750583648681641</v>
+        <v>0.9768059253692627</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
@@ -6484,25 +6484,25 @@
         <v>128</v>
       </c>
       <c r="N44" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O44" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O44" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P44" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q44" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R44" s="2" t="n">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="S44" s="2" t="n">
-        <v>55580</v>
+        <v>47797</v>
       </c>
       <c r="T44" s="2" t="n">
-        <v>0.06750583648681641</v>
+        <v>0.9768059253692627</v>
       </c>
       <c r="U44" s="2" t="b">
         <v>1</v>
@@ -6513,19 +6513,19 @@
         </is>
       </c>
       <c r="W44" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X44" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z44" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB44" s="2" t="n">
         <v>1</v>
@@ -6540,43 +6540,43 @@
         <v>4</v>
       </c>
       <c r="AF44" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG44" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH44" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI44" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0cccb810000a3ce</t>
+          <t>056411c401000200c35ad9c9013c02063c03063c04068c6b</t>
         </is>
       </c>
       <c r="AJ44" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK44" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL44" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM44" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN44" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO44" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP44" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="45">
@@ -6589,19 +6589,19 @@
         <v>44</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>1781814751.411194</v>
+        <v>1781983112.720179</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>21.45746302604675</v>
+        <v>21.88261914253235</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.9515731334686279</v>
+        <v>0.2548081874847412</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
@@ -6622,25 +6622,25 @@
         <v>128</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P45" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q45" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R45" s="2" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="S45" s="2" t="n">
-        <v>13750</v>
+        <v>25082</v>
       </c>
       <c r="T45" s="2" t="n">
-        <v>0.9515731334686279</v>
+        <v>0.2548081874847412</v>
       </c>
       <c r="U45" s="2" t="b">
         <v>1</v>
@@ -6651,19 +6651,19 @@
         </is>
       </c>
       <c r="W45" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X45" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y45" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z45" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA45" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB45" s="2" t="n">
         <v>1</v>
@@ -6678,43 +6678,43 @@
         <v>4</v>
       </c>
       <c r="AF45" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG45" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH45" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI45" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35acccc013c02063c03063c0406ef72</t>
+          <t>05640a440200010010f0dac98100008c66</t>
         </is>
       </c>
       <c r="AJ45" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK45" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL45" s="2" t="n">
-        <v>0.57</v>
+        <v>0.13</v>
       </c>
       <c r="AM45" s="2" t="n">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="AN45" s="2" t="n">
-        <v>0.34</v>
+        <v>0.04</v>
       </c>
       <c r="AO45" s="2" t="n">
-        <v>0.04</v>
+        <v>0.25</v>
       </c>
       <c r="AP45" s="2" t="n">
-        <v>0.02</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="46">
@@ -6727,19 +6727,19 @@
         <v>45</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>1781814751.711142</v>
+        <v>1781983113.527077</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>21.75741100311279</v>
+        <v>22.6895170211792</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.29994797706604</v>
+        <v>0.8068978786468506</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
@@ -6760,25 +6760,25 @@
         <v>128</v>
       </c>
       <c r="N46" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O46" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O46" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P46" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q46" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R46" s="2" t="n">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="S46" s="2" t="n">
-        <v>27335</v>
+        <v>63438</v>
       </c>
       <c r="T46" s="2" t="n">
-        <v>0.29994797706604</v>
+        <v>0.8068978786468506</v>
       </c>
       <c r="U46" s="2" t="b">
         <v>1</v>
@@ -6789,19 +6789,19 @@
         </is>
       </c>
       <c r="W46" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X46" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z46" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA46" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB46" s="2" t="n">
         <v>1</v>
@@ -6816,43 +6816,43 @@
         <v>4</v>
       </c>
       <c r="AF46" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG46" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH46" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI46" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0cdcc810000cf3b</t>
+          <t>056411c401000200c35adaca013c02063c03063c04064e28</t>
         </is>
       </c>
       <c r="AJ46" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK46" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL46" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM46" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN46" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO46" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP46" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="47">
@@ -6865,19 +6865,19 @@
         <v>46</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>1781814752.421401</v>
+        <v>1781983113.637784</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>22.46766996383667</v>
+        <v>22.80022406578064</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.710258960723877</v>
+        <v>0.1107070446014404</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
@@ -6898,25 +6898,25 @@
         <v>128</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P47" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q47" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="S47" s="2" t="n">
-        <v>40310</v>
+        <v>30609</v>
       </c>
       <c r="T47" s="2" t="n">
-        <v>0.710258960723877</v>
+        <v>0.1107070446014404</v>
       </c>
       <c r="U47" s="2" t="b">
         <v>1</v>
@@ -6927,19 +6927,19 @@
         </is>
       </c>
       <c r="W47" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X47" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y47" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z47" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA47" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB47" s="2" t="n">
         <v>1</v>
@@ -6954,43 +6954,43 @@
         <v>4</v>
       </c>
       <c r="AF47" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG47" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH47" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI47" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35acdcd013c02063c03063c04068688</t>
+          <t>05640a440200010010f0dbca810000cb4f</t>
         </is>
       </c>
       <c r="AJ47" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK47" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>CONTROL_ATTACK</t>
         </is>
       </c>
       <c r="AL47" s="2" t="n">
-        <v>0.57</v>
+        <v>0.28</v>
       </c>
       <c r="AM47" s="2" t="n">
-        <v>0.03</v>
+        <v>0.37</v>
       </c>
       <c r="AN47" s="2" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="AO47" s="2" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="AP47" s="2" t="n">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="48">
@@ -7003,19 +7003,19 @@
         <v>47</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>1781814752.640165</v>
+        <v>1781983114.558187</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>22.68643403053284</v>
+        <v>23.72062706947327</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.218764066696167</v>
+        <v>0.920403003692627</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
@@ -7036,25 +7036,25 @@
         <v>128</v>
       </c>
       <c r="N48" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O48" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O48" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P48" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q48" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R48" s="2" t="n">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="S48" s="2" t="n">
-        <v>2367</v>
+        <v>7419</v>
       </c>
       <c r="T48" s="2" t="n">
-        <v>0.218764066696167</v>
+        <v>0.920403003692627</v>
       </c>
       <c r="U48" s="2" t="b">
         <v>1</v>
@@ -7065,19 +7065,19 @@
         </is>
       </c>
       <c r="W48" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X48" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z48" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z48" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA48" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB48" s="2" t="n">
         <v>1</v>
@@ -7092,43 +7092,43 @@
         <v>4</v>
       </c>
       <c r="AF48" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG48" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH48" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI48" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0cecd8100002d9c</t>
+          <t>056411c401000200c35adbcb013c02063c03063c040627d2</t>
         </is>
       </c>
       <c r="AJ48" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK48" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL48" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM48" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN48" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO48" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP48" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="49">
@@ -7141,19 +7141,19 @@
         <v>48</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>1781814753.463887</v>
+        <v>1781983114.622964</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>23.51015591621399</v>
+        <v>23.78540396690369</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.8237218856811523</v>
+        <v>0.06477689743041992</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
@@ -7174,25 +7174,25 @@
         <v>128</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P49" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q49" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R49" s="2" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="S49" s="2" t="n">
-        <v>56841</v>
+        <v>25089</v>
       </c>
       <c r="T49" s="2" t="n">
-        <v>0.8237218856811523</v>
+        <v>0.06477689743041992</v>
       </c>
       <c r="U49" s="2" t="b">
         <v>1</v>
@@ -7203,19 +7203,19 @@
         </is>
       </c>
       <c r="W49" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X49" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y49" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z49" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB49" s="2" t="n">
         <v>1</v>
@@ -7230,43 +7230,43 @@
         <v>4</v>
       </c>
       <c r="AF49" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG49" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH49" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI49" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35acece013c02063c03063c040644cb</t>
+          <t>05640a440200010010f0dccb8100003164</t>
         </is>
       </c>
       <c r="AJ49" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK49" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>CONTROL_ATTACK</t>
         </is>
       </c>
       <c r="AL49" s="2" t="n">
-        <v>0.57</v>
+        <v>0.29</v>
       </c>
       <c r="AM49" s="2" t="n">
-        <v>0.03</v>
+        <v>0.36</v>
       </c>
       <c r="AN49" s="2" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="AO49" s="2" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="AP49" s="2" t="n">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="50">
@@ -7279,19 +7279,19 @@
         <v>49</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>1781814753.540908</v>
+        <v>1781983115.558275</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>23.58717703819275</v>
+        <v>24.72071504592896</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.07702112197875977</v>
+        <v>0.9353110790252686</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr"/>
@@ -7312,25 +7312,25 @@
         <v>128</v>
       </c>
       <c r="N50" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O50" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O50" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P50" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q50" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R50" s="2" t="n">
-        <v>182</v>
+        <v>234</v>
       </c>
       <c r="S50" s="2" t="n">
-        <v>61143</v>
+        <v>30963</v>
       </c>
       <c r="T50" s="2" t="n">
-        <v>0.07702112197875977</v>
+        <v>0.9353110790252686</v>
       </c>
       <c r="U50" s="2" t="b">
         <v>1</v>
@@ -7341,19 +7341,19 @@
         </is>
       </c>
       <c r="W50" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X50" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z50" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA50" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB50" s="2" t="n">
         <v>1</v>
@@ -7368,43 +7368,43 @@
         <v>4</v>
       </c>
       <c r="AF50" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG50" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH50" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI50" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0cfce8100006ab5</t>
+          <t>056411c401000200c35adccc013c02063c03063c0406caaf</t>
         </is>
       </c>
       <c r="AJ50" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK50" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL50" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM50" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN50" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO50" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP50" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="51">
@@ -7417,19 +7417,19 @@
         <v>50</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>1781814754.509898</v>
+        <v>1781983115.619429</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>24.55616688728333</v>
+        <v>24.78186917304993</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.9689898490905762</v>
+        <v>0.06115412712097168</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
@@ -7450,25 +7450,25 @@
         <v>128</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P51" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q51" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R51" s="2" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="S51" s="2" t="n">
-        <v>62585</v>
+        <v>13227</v>
       </c>
       <c r="T51" s="2" t="n">
-        <v>0.9689898490905762</v>
+        <v>0.06115412712097168</v>
       </c>
       <c r="U51" s="2" t="b">
         <v>1</v>
@@ -7479,19 +7479,19 @@
         </is>
       </c>
       <c r="W51" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X51" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y51" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z51" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA51" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB51" s="2" t="n">
         <v>1</v>
@@ -7506,43 +7506,43 @@
         <v>4</v>
       </c>
       <c r="AF51" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG51" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH51" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI51" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35acfcf013c02063c03063c04062d31</t>
+          <t>05640a440200010010f0ddcc8100005d91</t>
         </is>
       </c>
       <c r="AJ51" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK51" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>CONTROL_ATTACK</t>
         </is>
       </c>
       <c r="AL51" s="2" t="n">
-        <v>0.57</v>
+        <v>0.29</v>
       </c>
       <c r="AM51" s="2" t="n">
-        <v>0.03</v>
+        <v>0.36</v>
       </c>
       <c r="AN51" s="2" t="n">
-        <v>0.34</v>
+        <v>0.06</v>
       </c>
       <c r="AO51" s="2" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="AP51" s="2" t="n">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="52">
@@ -7555,19 +7555,19 @@
         <v>51</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>1781814754.761387</v>
+        <v>1781983116.610833</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>24.80765604972839</v>
+        <v>25.77327299118042</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.2514891624450684</v>
+        <v>0.9914038181304932</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H52" s="2" t="inlineStr"/>
       <c r="I52" s="2" t="inlineStr"/>
@@ -7588,25 +7588,25 @@
         <v>128</v>
       </c>
       <c r="N52" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O52" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O52" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P52" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q52" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R52" s="2" t="n">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="S52" s="2" t="n">
-        <v>16845</v>
+        <v>40740</v>
       </c>
       <c r="T52" s="2" t="n">
-        <v>0.2514891624450684</v>
+        <v>0.9914038181304932</v>
       </c>
       <c r="U52" s="2" t="b">
         <v>1</v>
@@ -7617,19 +7617,19 @@
         </is>
       </c>
       <c r="W52" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X52" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z52" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z52" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB52" s="2" t="n">
         <v>1</v>
@@ -7644,43 +7644,43 @@
         <v>4</v>
       </c>
       <c r="AF52" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG52" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH52" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI52" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0d0cf8100004b61</t>
+          <t>056411c401000200c35addcd013c02063c03063c0406a355</t>
         </is>
       </c>
       <c r="AJ52" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK52" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL52" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM52" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN52" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO52" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP52" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="53">
@@ -7693,19 +7693,19 @@
         <v>52</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>1781814755.545679</v>
+        <v>1781983116.894785</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>25.59194803237915</v>
+        <v>26.05722498893738</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.7842919826507568</v>
+        <v>0.283951997756958</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H53" s="2" t="inlineStr"/>
       <c r="I53" s="2" t="inlineStr"/>
@@ -7726,25 +7726,25 @@
         <v>128</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P53" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q53" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R53" s="2" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="S53" s="2" t="n">
-        <v>25763</v>
+        <v>36127</v>
       </c>
       <c r="T53" s="2" t="n">
-        <v>0.7842919826507568</v>
+        <v>0.283951997756958</v>
       </c>
       <c r="U53" s="2" t="b">
         <v>1</v>
@@ -7755,19 +7755,19 @@
         </is>
       </c>
       <c r="W53" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X53" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y53" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z53" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA53" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB53" s="2" t="n">
         <v>1</v>
@@ -7782,43 +7782,43 @@
         <v>4</v>
       </c>
       <c r="AF53" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG53" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH53" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI53" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ad0c0013c02063c03063c0406bbed</t>
+          <t>05640a440200010010f0decd810000bf36</t>
         </is>
       </c>
       <c r="AJ53" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK53" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL53" s="2" t="n">
-        <v>0.57</v>
+        <v>0.13</v>
       </c>
       <c r="AM53" s="2" t="n">
-        <v>0.03</v>
+        <v>0.17</v>
       </c>
       <c r="AN53" s="2" t="n">
-        <v>0.34</v>
+        <v>0.04</v>
       </c>
       <c r="AO53" s="2" t="n">
-        <v>0.04</v>
+        <v>0.25</v>
       </c>
       <c r="AP53" s="2" t="n">
-        <v>0.02</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="54">
@@ -7831,19 +7831,19 @@
         <v>53</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>1781814755.665819</v>
+        <v>1781983117.660087</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>25.71208786964417</v>
+        <v>26.82252717018127</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>0.1201398372650146</v>
+        <v>0.7653021812438965</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
       <c r="I54" s="2" t="inlineStr"/>
@@ -7864,25 +7864,25 @@
         <v>128</v>
       </c>
       <c r="N54" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O54" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O54" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P54" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q54" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R54" s="2" t="n">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="S54" s="2" t="n">
-        <v>16630</v>
+        <v>57401</v>
       </c>
       <c r="T54" s="2" t="n">
-        <v>0.1201398372650146</v>
+        <v>0.7653021812438965</v>
       </c>
       <c r="U54" s="2" t="b">
         <v>1</v>
@@ -7893,19 +7893,19 @@
         </is>
       </c>
       <c r="W54" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X54" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z54" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z54" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA54" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB54" s="2" t="n">
         <v>1</v>
@@ -7920,43 +7920,43 @@
         <v>4</v>
       </c>
       <c r="AF54" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG54" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH54" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI54" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0d1c08100000861</t>
+          <t>056411c401000200c35adece013c02063c03063c04066116</t>
         </is>
       </c>
       <c r="AJ54" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK54" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL54" s="2" t="n">
-        <v>0.86</v>
+        <v>0.08</v>
       </c>
       <c r="AM54" s="2" t="n">
-        <v>0.04</v>
+        <v>0.23</v>
       </c>
       <c r="AN54" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO54" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP54" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="55">
@@ -7969,19 +7969,19 @@
         <v>54</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1781814756.593214</v>
+        <v>1781983117.801831</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>26.6394829750061</v>
+        <v>26.964271068573</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.9273951053619385</v>
+        <v>0.1417438983917236</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H55" s="2" t="inlineStr"/>
       <c r="I55" s="2" t="inlineStr"/>
@@ -8002,25 +8002,25 @@
         <v>128</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P55" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q55" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R55" s="2" t="n">
-        <v>195</v>
+        <v>229</v>
       </c>
       <c r="S55" s="2" t="n">
-        <v>19791</v>
+        <v>41660</v>
       </c>
       <c r="T55" s="2" t="n">
-        <v>0.9273951053619385</v>
+        <v>0.1417438983917236</v>
       </c>
       <c r="U55" s="2" t="b">
         <v>1</v>
@@ -8031,19 +8031,19 @@
         </is>
       </c>
       <c r="W55" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X55" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y55" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z55" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA55" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB55" s="2" t="n">
         <v>1</v>
@@ -8058,43 +8058,43 @@
         <v>4</v>
       </c>
       <c r="AF55" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG55" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH55" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI55" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ad1c1013c02063c03063c0406d217</t>
+          <t>05640a440200010010f0dfce810000f81f</t>
         </is>
       </c>
       <c r="AJ55" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK55" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>CONTROL_ATTACK</t>
         </is>
       </c>
       <c r="AL55" s="2" t="n">
-        <v>0.57</v>
+        <v>0.26</v>
       </c>
       <c r="AM55" s="2" t="n">
-        <v>0.03</v>
+        <v>0.33</v>
       </c>
       <c r="AN55" s="2" t="n">
-        <v>0.34</v>
+        <v>0.05</v>
       </c>
       <c r="AO55" s="2" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="AP55" s="2" t="n">
-        <v>0.02</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="56">
@@ -8107,19 +8107,19 @@
         <v>55</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1781814756.653243</v>
+        <v>1781983118.678163</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>26.69951200485229</v>
+        <v>27.84060311317444</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.06002902984619141</v>
+        <v>0.8763320446014404</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
       <c r="I56" s="2" t="inlineStr"/>
@@ -8140,25 +8140,25 @@
         <v>128</v>
       </c>
       <c r="N56" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O56" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O56" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P56" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q56" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R56" s="2" t="n">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="S56" s="2" t="n">
-        <v>55785</v>
+        <v>14138</v>
       </c>
       <c r="T56" s="2" t="n">
-        <v>0.06002902984619141</v>
+        <v>0.8763320446014404</v>
       </c>
       <c r="U56" s="2" t="b">
         <v>1</v>
@@ -8169,19 +8169,19 @@
         </is>
       </c>
       <c r="W56" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X56" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z56" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z56" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA56" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB56" s="2" t="n">
         <v>1</v>
@@ -8196,43 +8196,43 @@
         <v>4</v>
       </c>
       <c r="AF56" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG56" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH56" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI56" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0d2c1810000eac6</t>
+          <t>056411c401000200c35adfcf013c02063c03063c040608ec</t>
         </is>
       </c>
       <c r="AJ56" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK56" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL56" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM56" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN56" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO56" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP56" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="57">
@@ -8245,19 +8245,19 @@
         <v>56</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>1781814757.64206</v>
+        <v>1781983118.73557</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>27.68832898139954</v>
+        <v>27.89801001548767</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.9888169765472412</v>
+        <v>0.05740690231323242</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
       <c r="I57" s="2" t="inlineStr"/>
@@ -8278,25 +8278,25 @@
         <v>128</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P57" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q57" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R57" s="2" t="n">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="S57" s="2" t="n">
-        <v>3561</v>
+        <v>60934</v>
       </c>
       <c r="T57" s="2" t="n">
-        <v>0.9888169765472412</v>
+        <v>0.05740690231323242</v>
       </c>
       <c r="U57" s="2" t="b">
         <v>1</v>
@@ -8307,19 +8307,19 @@
         </is>
       </c>
       <c r="W57" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X57" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y57" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA57" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB57" s="2" t="n">
         <v>1</v>
@@ -8334,43 +8334,43 @@
         <v>4</v>
       </c>
       <c r="AF57" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG57" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH57" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI57" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ad2c2013c02063c03063c04061054</t>
+          <t>05640a440200010010f0e0cf81000084d3</t>
         </is>
       </c>
       <c r="AJ57" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK57" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>CONTROL_ATTACK</t>
         </is>
       </c>
       <c r="AL57" s="2" t="n">
-        <v>0.57</v>
+        <v>0.29</v>
       </c>
       <c r="AM57" s="2" t="n">
-        <v>0.03</v>
+        <v>0.48</v>
       </c>
       <c r="AN57" s="2" t="n">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="AO57" s="2" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="AP57" s="2" t="n">
-        <v>0.02</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="58">
@@ -8383,19 +8383,19 @@
         <v>57</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>1781814757.866946</v>
+        <v>1781983119.729138</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>27.91321492195129</v>
+        <v>28.89157795906067</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0.2248859405517578</v>
+        <v>0.993567943572998</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="2" t="inlineStr"/>
@@ -8416,25 +8416,25 @@
         <v>128</v>
       </c>
       <c r="N58" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O58" s="2" t="n">
         <v>20003</v>
       </c>
-      <c r="O58" s="2" t="n">
-        <v>57678</v>
-      </c>
       <c r="P58" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q58" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="R58" s="2" t="n">
-        <v>182</v>
+        <v>233</v>
       </c>
       <c r="S58" s="2" t="n">
-        <v>45052</v>
+        <v>37188</v>
       </c>
       <c r="T58" s="2" t="n">
-        <v>0.2248859405517578</v>
+        <v>0.993567943572998</v>
       </c>
       <c r="U58" s="2" t="b">
         <v>1</v>
@@ -8445,19 +8445,19 @@
         </is>
       </c>
       <c r="W58" s="2" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="X58" s="2" t="n">
-        <v>68</v>
+        <v>196</v>
       </c>
       <c r="Y58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z58" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="Z58" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA58" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB58" s="2" t="n">
         <v>1</v>
@@ -8472,43 +8472,43 @@
         <v>4</v>
       </c>
       <c r="AF58" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AG58" s="2" t="inlineStr">
         <is>
-          <t>RESPONSE</t>
+          <t>READ</t>
         </is>
       </c>
       <c r="AH58" s="2" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AI58" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0d3c2810000adef</t>
+          <t>056411c401000200c35ae0c0013c02063c03063c0406adc7</t>
         </is>
       </c>
       <c r="AJ58" s="2" t="n">
-        <v>129</v>
+        <v>1</v>
       </c>
       <c r="AK58" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL58" s="2" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="AM58" s="2" t="n">
-        <v>0.04</v>
+        <v>0.22</v>
       </c>
       <c r="AN58" s="2" t="n">
-        <v>0.01</v>
+        <v>0.15</v>
       </c>
       <c r="AO58" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="AP58" s="2" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="59">
@@ -8521,19 +8521,19 @@
         <v>58</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>1781814758.665113</v>
+        <v>1781983120.011699</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>28.71138191223145</v>
+        <v>29.17413902282715</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.7981669902801514</v>
+        <v>0.2825610637664795</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="2" t="inlineStr"/>
@@ -8554,25 +8554,25 @@
         <v>128</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>57678</v>
+        <v>20003</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>20003</v>
+        <v>65130</v>
       </c>
       <c r="P59" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q59" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="R59" s="2" t="n">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="S59" s="2" t="n">
-        <v>41828</v>
+        <v>60585</v>
       </c>
       <c r="T59" s="2" t="n">
-        <v>0.7981669902801514</v>
+        <v>0.2825610637664795</v>
       </c>
       <c r="U59" s="2" t="b">
         <v>1</v>
@@ -8583,19 +8583,19 @@
         </is>
       </c>
       <c r="W59" s="2" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="X59" s="2" t="n">
-        <v>196</v>
+        <v>68</v>
       </c>
       <c r="Y59" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z59" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AA59" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB59" s="2" t="n">
         <v>1</v>
@@ -8610,457 +8610,43 @@
         <v>4</v>
       </c>
       <c r="AF59" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AG59" s="2" t="inlineStr">
         <is>
-          <t>READ</t>
+          <t>RESPONSE</t>
         </is>
       </c>
       <c r="AH59" s="2" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AI59" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ad3c3013c02063c03063c040679ae</t>
+          <t>05640a440200010010f0e1c0810000c7d3</t>
         </is>
       </c>
       <c r="AJ59" s="2" t="n">
-        <v>1</v>
+        <v>129</v>
       </c>
       <c r="AK59" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DOS_ATTACK</t>
         </is>
       </c>
       <c r="AL59" s="2" t="n">
-        <v>0.57</v>
+        <v>0.12</v>
       </c>
       <c r="AM59" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="AN59" s="2" t="n">
-        <v>0.34</v>
+        <v>0.01</v>
       </c>
       <c r="AO59" s="2" t="n">
-        <v>0.04</v>
+        <v>0.25</v>
       </c>
       <c r="AP59" s="2" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>live_capture</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>1781814758.794352</v>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>28.84062099456787</v>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>0.1292390823364258</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M60" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="N60" s="2" t="n">
-        <v>20003</v>
-      </c>
-      <c r="O60" s="2" t="n">
-        <v>57678</v>
-      </c>
-      <c r="P60" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q60" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="R60" s="2" t="n">
-        <v>181</v>
-      </c>
-      <c r="S60" s="2" t="n">
-        <v>55849</v>
-      </c>
-      <c r="T60" s="2" t="n">
-        <v>0.1292390823364258</v>
-      </c>
-      <c r="U60" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>0x0564</t>
-        </is>
-      </c>
-      <c r="W60" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="X60" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="Y60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE60" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF60" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="AG60" s="2" t="inlineStr">
-        <is>
-          <t>RESPONSE</t>
-        </is>
-      </c>
-      <c r="AH60" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI60" s="2" t="inlineStr">
-        <is>
-          <t>05640a440200010010f0d4c381000057c4</t>
-        </is>
-      </c>
-      <c r="AJ60" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="AK60" s="2" t="inlineStr">
-        <is>
-          <t>RESTART_ATTACK</t>
-        </is>
-      </c>
-      <c r="AL60" s="2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AM60" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AN60" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AO60" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AP60" s="2" t="n">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>live_capture</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>1781814759.7132</v>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>29.7594690322876</v>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>0.9188480377197266</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M61" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="N61" s="2" t="n">
-        <v>57678</v>
-      </c>
-      <c r="O61" s="2" t="n">
-        <v>20003</v>
-      </c>
-      <c r="P61" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q61" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="R61" s="2" t="n">
-        <v>194</v>
-      </c>
-      <c r="S61" s="2" t="n">
-        <v>34582</v>
-      </c>
-      <c r="T61" s="2" t="n">
-        <v>0.9188480377197266</v>
-      </c>
-      <c r="U61" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V61" s="2" t="inlineStr">
-        <is>
-          <t>0x0564</t>
-        </is>
-      </c>
-      <c r="W61" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="X61" s="2" t="n">
-        <v>196</v>
-      </c>
-      <c r="Y61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG61" s="2" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-      <c r="AH61" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI61" s="2" t="inlineStr">
-        <is>
-          <t>056411c401000200c35ad4c4013c02063c03063c040694d3</t>
-        </is>
-      </c>
-      <c r="AJ61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK61" s="2" t="inlineStr">
-        <is>
-          <t>RESTART_ATTACK</t>
-        </is>
-      </c>
-      <c r="AL61" s="2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="AM61" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AN61" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="AO61" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AP61" s="2" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>live_capture</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>1781814759.778931</v>
-      </c>
-      <c r="D62" s="2" t="n">
-        <v>29.825199842453</v>
-      </c>
-      <c r="E62" s="2" t="n">
-        <v>0.06573081016540527</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="G62" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="2" t="inlineStr"/>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M62" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="N62" s="2" t="n">
-        <v>20003</v>
-      </c>
-      <c r="O62" s="2" t="n">
-        <v>57678</v>
-      </c>
-      <c r="P62" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q62" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="R62" s="2" t="n">
-        <v>181</v>
-      </c>
-      <c r="S62" s="2" t="n">
-        <v>27676</v>
-      </c>
-      <c r="T62" s="2" t="n">
-        <v>0.06573081016540527</v>
-      </c>
-      <c r="U62" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V62" s="2" t="inlineStr">
-        <is>
-          <t>0x0564</t>
-        </is>
-      </c>
-      <c r="W62" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="X62" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="Y62" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB62" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD62" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE62" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF62" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="AG62" s="2" t="inlineStr">
-        <is>
-          <t>RESPONSE</t>
-        </is>
-      </c>
-      <c r="AH62" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI62" s="2" t="inlineStr">
-        <is>
-          <t>05640a440200010010f0d5c48100003b31</t>
-        </is>
-      </c>
-      <c r="AJ62" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="AK62" s="2" t="inlineStr">
-        <is>
-          <t>RESTART_ATTACK</t>
-        </is>
-      </c>
-      <c r="AL62" s="2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AM62" s="2" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="AN62" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AO62" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AP62" s="2" t="n">
-        <v>0.06</v>
+        <v>0.38</v>
       </c>
     </row>
   </sheetData>
